--- a/app/reports/HCA_research.xlsx
+++ b/app/reports/HCA_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-26 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-27 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>391.4225</v>
+        <v>391.68</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.297</v>
+        <v>0.296</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.797</v>
+        <v>0.796</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.04372</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>221839793.2259898</v>
+        <v>221839811.7647059</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>391.4225</v>
+        <v>391.68</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>86833086464</v>
+        <v>86890217472</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>13.49</v>
+        <v>13.5</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>8.859999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>116275535872</v>
+        <v>117459943424</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>15.94958</v>
+        <v>16.112045</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>7.857</v>
+        <v>8.087</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>3.075</v>
+        <v>3.165</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>133570445312</v>
+        <v>133130248192</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>45.914474</v>
+        <v>45.563316</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>12.994</v>
+        <v>12.967</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>0.494</v>
+        <v>0.493</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>104603361280</v>
+        <v>105174310912</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>13.924</v>
+        <v>14.037433</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>10.456</v>
+        <v>10.563</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>3.647</v>
+        <v>3.684</v>
       </c>
     </row>
     <row r="9">
@@ -1616,13 +1616,13 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>90251132928</v>
+        <v>89390030848</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>20.106024</v>
+        <v>19.883072</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>14.23</v>
+        <v>14.225</v>
       </c>
       <c r="F9" s="34" t="n">
         <v>0.243</v>
@@ -1640,16 +1640,16 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>103568457728</v>
+        <v>103658061824</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>21.69169</v>
+        <v>21.710457</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>12.235</v>
+        <v>12.293</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>3.399</v>
+        <v>3.415</v>
       </c>
     </row>
     <row r="11">
@@ -1664,16 +1664,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>137356607488</v>
+        <v>138439507968</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>18.396948</v>
+        <v>18.541986</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>7.339</v>
+        <v>7.478</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>2.951</v>
+        <v>3.007</v>
       </c>
     </row>
     <row r="12">
@@ -1688,16 +1688,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>101866840064</v>
+        <v>102812377088</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>18.913334</v>
+        <v>19.08889</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>9.003</v>
+        <v>9.218999999999999</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>2.439</v>
+        <v>2.497</v>
       </c>
     </row>
     <row r="13">
@@ -1712,16 +1712,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>126585733120</v>
+        <v>127547957248</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>38.26188</v>
+        <v>38.463585</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>19.291</v>
+        <v>20.211</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>5.281</v>
+        <v>5.533</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/HCA_research.xlsx
+++ b/app/reports/HCA_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-27 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-28 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04372</v>
+        <v>0.04372000217437744</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/HCA_research.xlsx
+++ b/app/reports/HCA_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-28 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-29 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>507.78</v>
+        <v>507.32</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>391.68</v>
+        <v>391.15</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.296</v>
+        <v>0.297</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.796</v>
+        <v>0.797</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.04375999927520752</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>221839811.7647059</v>
+        <v>221839799.8108143</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>391.68</v>
+        <v>391.15</v>
       </c>
     </row>
     <row r="38">
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>86890217472</v>
+        <v>86772637696</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>13.5</v>
+        <v>13.48</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>8.93</v>
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>117459943424</v>
+        <v>117837725696</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>16.112045</v>
+        <v>16.163866</v>
       </c>
       <c r="E6" s="34" t="n">
         <v>8.087</v>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>133130248192</v>
+        <v>132345552896</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>45.563316</v>
+        <v>45.29476</v>
       </c>
       <c r="E7" s="34" t="n">
         <v>12.967</v>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>105174310912</v>
+        <v>105054109696</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>14.037433</v>
+        <v>14.02139</v>
       </c>
       <c r="E8" s="34" t="n">
         <v>10.563</v>
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>89390030848</v>
+        <v>88123244544</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>19.883072</v>
+        <v>19.601301</v>
       </c>
       <c r="E9" s="34" t="n">
         <v>14.225</v>
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>103658061824</v>
+        <v>104118870016</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>21.710457</v>
+        <v>21.806969</v>
       </c>
       <c r="E10" s="34" t="n">
         <v>12.293</v>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>138439507968</v>
+        <v>138012049408</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>18.541986</v>
+        <v>18.484734</v>
       </c>
       <c r="E11" s="34" t="n">
         <v>7.478</v>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>102812377088</v>
+        <v>103183409152</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>19.08889</v>
+        <v>19.157778</v>
       </c>
       <c r="E12" s="34" t="n">
         <v>9.218999999999999</v>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>127547957248</v>
+        <v>127915991040</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>38.463585</v>
+        <v>38.57457</v>
       </c>
       <c r="E13" s="34" t="n">
         <v>20.211</v>

--- a/app/reports/HCA_research.xlsx
+++ b/app/reports/HCA_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-29 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-30 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.83</v>
+        <v>0.829</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>507.32</v>
+        <v>503.47</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>391.15</v>
+        <v>388.705</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.297</v>
+        <v>0.295</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.797</v>
+        <v>0.795</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04375999927520752</v>
+        <v>0.04409999847412109</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>221839799.8108143</v>
+        <v>221839794.1472325</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>391.15</v>
+        <v>388.705</v>
       </c>
     </row>
     <row r="38">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>86772637696</v>
+        <v>86230237184</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>13.48</v>
+        <v>13.39</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>8.93</v>
+        <v>8.94</v>
       </c>
       <c r="F5" s="32" t="n">
         <v>1.82</v>
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>117837725696</v>
+        <v>118338035712</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>16.163866</v>
+        <v>16.232494</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>8.087</v>
+        <v>8.199</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>3.165</v>
+        <v>3.209</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>132345552896</v>
+        <v>132428496896</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>45.29476</v>
+        <v>45.52193</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>12.967</v>
+        <v>12.905</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>0.493</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>105054109696</v>
+        <v>105194340352</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>14.02139</v>
+        <v>14.002666</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>10.563</v>
+        <v>10.617</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>3.684</v>
+        <v>3.703</v>
       </c>
     </row>
     <row r="9">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>88123244544</v>
+        <v>88020803584</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>19.601301</v>
+        <v>19.604042</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>14.225</v>
+        <v>13.946</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>0.243</v>
+        <v>0.238</v>
       </c>
     </row>
     <row r="10">
@@ -1640,16 +1640,16 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>104118870016</v>
+        <v>101046771712</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>21.806969</v>
+        <v>21.16354</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>12.293</v>
+        <v>12.287</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>3.415</v>
+        <v>3.414</v>
       </c>
     </row>
     <row r="11">
@@ -1664,16 +1664,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>138012049408</v>
+        <v>137556082688</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>18.484734</v>
+        <v>18.423666</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>7.478</v>
+        <v>7.496</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>3.007</v>
+        <v>3.014</v>
       </c>
     </row>
     <row r="12">
@@ -1688,16 +1688,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>103183409152</v>
+        <v>102596935680</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>19.157778</v>
+        <v>19.04889</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>9.218999999999999</v>
+        <v>9.308999999999999</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>2.497</v>
+        <v>2.522</v>
       </c>
     </row>
     <row r="13">
@@ -1712,16 +1712,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>127915991040</v>
+        <v>119963164672</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>38.57457</v>
+        <v>36.260136</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>20.211</v>
+        <v>20.089</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>5.533</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/HCA_research.xlsx
+++ b/app/reports/HCA_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-30 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-01 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.829</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>503.47</v>
+        <v>497.1</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>388.705</v>
+        <v>391.985</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.295</v>
+        <v>0.268</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.795</v>
+        <v>0.768</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04409999847412109</v>
+        <v>0.04467000007629394</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>221839794.1472325</v>
+        <v>221839803.0536883</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>388.705</v>
+        <v>391.985</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>86230237184</v>
+        <v>86957875200</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>13.39</v>
+        <v>13.49</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>8.94</v>
+        <v>8.9</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>118338035712</v>
+        <v>115315769344</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>16.232494</v>
+        <v>15.817927</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>8.199</v>
+        <v>8.097</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>3.209</v>
+        <v>3.169</v>
       </c>
     </row>
     <row r="7">
@@ -1568,13 +1568,13 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>132428496896</v>
+        <v>133319467008</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>45.52193</v>
+        <v>45.8282</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>12.905</v>
+        <v>12.894</v>
       </c>
       <c r="F7" s="34" t="n">
         <v>0.49</v>
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>105194340352</v>
+        <v>102413058048</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>14.002666</v>
+        <v>13.636</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>10.617</v>
+        <v>10.549</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>3.703</v>
+        <v>3.679</v>
       </c>
     </row>
     <row r="9">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>88020803584</v>
+        <v>89853648896</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>19.604042</v>
+        <v>19.99661</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>13.946</v>
+        <v>14.087</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>0.238</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="10">
@@ -1640,16 +1640,16 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>101046771712</v>
+        <v>101353979904</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>21.16354</v>
+        <v>21.227882</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>12.287</v>
+        <v>11.945</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>3.414</v>
+        <v>3.319</v>
       </c>
     </row>
     <row r="11">
@@ -1664,16 +1664,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>137556082688</v>
+        <v>135903240192</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>18.423666</v>
+        <v>18.20229</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>7.496</v>
+        <v>7.431</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>3.014</v>
+        <v>2.988</v>
       </c>
     </row>
     <row r="12">
@@ -1688,16 +1688,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>102596935680</v>
+        <v>98970378240</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>19.04889</v>
+        <v>18.294249</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>9.308999999999999</v>
+        <v>9.164999999999999</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>2.522</v>
+        <v>2.482</v>
       </c>
     </row>
     <row r="13">
@@ -1712,16 +1712,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>119963164672</v>
+        <v>119545298944</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>36.260136</v>
+        <v>36.133835</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>20.089</v>
+        <v>19.22</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>5.5</v>
+        <v>5.262</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/HCA_research.xlsx
+++ b/app/reports/HCA_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-01 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-23 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>497.1</v>
+        <v>474.59</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>391.985</v>
+        <v>372.76</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.268</v>
+        <v>0.273</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.768</v>
+        <v>0.773</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04467000007629394</v>
+        <v>0.04699000358581543</v>
       </c>
     </row>
     <row r="6">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>1.134</v>
+        <v>1.128</v>
       </c>
     </row>
     <row r="8">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>221839803.0536883</v>
+        <v>221839803.92746</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>391.985</v>
+        <v>372.76</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>86957875200</v>
+        <v>82693005312</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>13.49</v>
+        <v>12.84</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>8.9</v>
+        <v>8.65</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>115315769344</v>
+        <v>125893697536</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>15.817927</v>
+        <v>17.268908</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>8.097</v>
+        <v>8.435</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>3.169</v>
+        <v>3.301</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>133319467008</v>
+        <v>135847976960</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>45.8282</v>
+        <v>46.69737</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>12.894</v>
+        <v>13.277</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>0.49</v>
+        <v>0.504</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>102413058048</v>
+        <v>101281480704</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>13.636</v>
+        <v>13.23822</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>10.549</v>
+        <v>10.257</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>3.679</v>
+        <v>3.577</v>
       </c>
     </row>
     <row r="9">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>89853648896</v>
+        <v>95601000448</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>19.99661</v>
+        <v>21.297861</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>14.087</v>
+        <v>15.107</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>0.24</v>
+        <v>0.258</v>
       </c>
     </row>
     <row r="10">
@@ -1640,16 +1640,16 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>101353979904</v>
+        <v>104720490496</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>21.227882</v>
+        <v>21.932976</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>11.945</v>
+        <v>12.408</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>3.319</v>
+        <v>3.447</v>
       </c>
     </row>
     <row r="11">
@@ -1664,16 +1664,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>135903240192</v>
+        <v>142286618624</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>18.20229</v>
+        <v>19.057253</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>7.431</v>
+        <v>7.597</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>2.988</v>
+        <v>3.055</v>
       </c>
     </row>
     <row r="12">
@@ -1688,16 +1688,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>98970378240</v>
+        <v>103805796352</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>18.294249</v>
+        <v>19.188053</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>9.164999999999999</v>
+        <v>9.377000000000001</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>2.482</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="13">
@@ -1712,16 +1712,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>119545298944</v>
+        <v>120214265856</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>36.133835</v>
+        <v>36.336037</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>19.22</v>
+        <v>18.91</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>5.262</v>
+        <v>5.177</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/HCA_research.xlsx
+++ b/app/reports/HCA_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-23 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-24 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.82</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>474.59</v>
+        <v>477.31</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>372.76</v>
+        <v>379.18</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.273</v>
+        <v>0.259</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.773</v>
+        <v>0.759</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04699000358581543</v>
+        <v>0.04672999858856201</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>221839803.92746</v>
+        <v>221839805.0530091</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>372.76</v>
+        <v>379.18</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>82693005312</v>
+        <v>84117217280</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>12.84</v>
+        <v>13.06</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>8.65</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>125893697536</v>
+        <v>126863679488</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>17.268908</v>
+        <v>17.40196</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>8.435</v>
+        <v>8.516</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>3.301</v>
+        <v>3.333</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>135847976960</v>
+        <v>137047359488</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>46.69737</v>
+        <v>47.10965</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>13.277</v>
+        <v>13.179</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>0.504</v>
+        <v>0.501</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>101281480704</v>
+        <v>102663405568</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>13.23822</v>
+        <v>13.489473</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>10.257</v>
+        <v>10.253</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>3.577</v>
+        <v>3.576</v>
       </c>
     </row>
     <row r="9">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>95601000448</v>
+        <v>97780989952</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>21.297861</v>
+        <v>21.783516</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>15.107</v>
+        <v>15.29</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>0.258</v>
+        <v>0.261</v>
       </c>
     </row>
     <row r="10">
@@ -1640,16 +1640,16 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>104720490496</v>
+        <v>106382893056</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>21.932976</v>
+        <v>22.281153</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>12.408</v>
+        <v>12.423</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>3.447</v>
+        <v>3.452</v>
       </c>
     </row>
     <row r="11">
@@ -1664,16 +1664,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>142286618624</v>
+        <v>140234817536</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>19.057253</v>
+        <v>18.782444</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>7.597</v>
+        <v>7.639</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>3.055</v>
+        <v>3.072</v>
       </c>
     </row>
     <row r="12">
@@ -1688,16 +1688,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>103805796352</v>
+        <v>103710040064</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>19.188053</v>
+        <v>19.170355</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>9.377000000000001</v>
+        <v>9.295999999999999</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>2.54</v>
+        <v>2.518</v>
       </c>
     </row>
     <row r="13">
@@ -1712,16 +1712,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>120214265856</v>
+        <v>126236868608</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>36.336037</v>
+        <v>38.112267</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>18.91</v>
+        <v>19.449</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>5.177</v>
+        <v>5.324</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/HCA_research.xlsx
+++ b/app/reports/HCA_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-24 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-25 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.858</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>477.31</v>
+        <v>522.63</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>379.18</v>
+        <v>382.19</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.259</v>
+        <v>0.367</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.759</v>
+        <v>0.867</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04672999858856201</v>
+        <v>0.04678999900817871</v>
       </c>
     </row>
     <row r="6">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>1.128</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>49844998144</v>
+        <v>51552002048</v>
       </c>
     </row>
     <row r="33">
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>1064000000</v>
+        <v>1013000000</v>
       </c>
     </row>
     <row r="34">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>221839805.0530091</v>
+        <v>221839805.8347942</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>379.18</v>
+        <v>382.19</v>
       </c>
     </row>
     <row r="38">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>84117217280</v>
+        <v>84784955392</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>13.06</v>
+        <v>12.82</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>8.710000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="F5" s="32" t="n">
         <v>1.78</v>
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>126863679488</v>
+        <v>126792204288</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>17.40196</v>
+        <v>17.392157</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>8.516</v>
+        <v>8.579000000000001</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>3.333</v>
+        <v>3.357</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>137047359488</v>
+        <v>137468411904</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>47.10965</v>
+        <v>47.254387</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>13.179</v>
+        <v>13.249</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>0.501</v>
+        <v>0.503</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>102663405568</v>
+        <v>102843662336</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>13.489473</v>
+        <v>13.513158</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>10.253</v>
+        <v>10.361</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>3.576</v>
+        <v>3.614</v>
       </c>
     </row>
     <row r="9">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>97780989952</v>
+        <v>98450677760</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>21.783516</v>
+        <v>21.92699</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>15.29</v>
+        <v>15.576</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>0.261</v>
+        <v>0.266</v>
       </c>
     </row>
     <row r="10">
@@ -1640,16 +1640,16 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>106382893056</v>
+        <v>106512556032</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>22.281153</v>
+        <v>22.308311</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>12.423</v>
+        <v>12.576</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>3.452</v>
+        <v>3.494</v>
       </c>
     </row>
     <row r="11">
@@ -1664,16 +1664,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>140234817536</v>
+        <v>139864358912</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>18.782444</v>
+        <v>18.732826</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>7.639</v>
+        <v>7.534</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>3.072</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="12">
@@ -1688,13 +1688,13 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>103710040064</v>
+        <v>103769882624</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>19.170355</v>
+        <v>19.181416</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>9.295999999999999</v>
+        <v>9.294</v>
       </c>
       <c r="F12" s="34" t="n">
         <v>2.518</v>
@@ -1712,16 +1712,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>126236868608</v>
+        <v>126604894208</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>38.112267</v>
+        <v>38.17919</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>19.449</v>
+        <v>20.074</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>5.324</v>
+        <v>5.496</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/HCA_research.xlsx
+++ b/app/reports/HCA_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-25 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-26 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.858</v>
+        <v>0.802</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>522.63</v>
+        <v>468.76</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.367</v>
+        <v>0.227</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.867</v>
+        <v>0.726</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>1</v>
+        <v>1.128</v>
       </c>
     </row>
     <row r="8">

--- a/app/reports/HCA_research.xlsx
+++ b/app/reports/HCA_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-26 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-27 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.802</v>
+        <v>0.798</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>468.76</v>
+        <v>472.12</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>382.19</v>
+        <v>388.11</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.227</v>
+        <v>0.216</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.726</v>
+        <v>0.716</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04678999900817871</v>
+        <v>0.04647000312805176</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>221839805.8347942</v>
+        <v>221839807.4772616</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>382.19</v>
+        <v>388.11</v>
       </c>
     </row>
     <row r="38">
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>84784955392</v>
+        <v>86098247680</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>12.82</v>
+        <v>13.02</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>8.84</v>
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>126792204288</v>
+        <v>128068501504</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>17.392157</v>
+        <v>17.567226</v>
       </c>
       <c r="E6" s="34" t="n">
         <v>8.579000000000001</v>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>137468411904</v>
+        <v>136192475136</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>47.254387</v>
+        <v>46.81579</v>
       </c>
       <c r="E7" s="34" t="n">
         <v>13.249</v>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>102843662336</v>
+        <v>104586100736</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>13.513158</v>
+        <v>13.7421055</v>
       </c>
       <c r="E8" s="34" t="n">
         <v>10.361</v>
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>98450677760</v>
+        <v>100020101120</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>21.92699</v>
+        <v>22.276533</v>
       </c>
       <c r="E9" s="34" t="n">
         <v>15.576</v>
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>106512556032</v>
+        <v>108605431808</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>22.308311</v>
+        <v>22.746649</v>
       </c>
       <c r="E10" s="34" t="n">
         <v>12.576</v>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>139864358912</v>
+        <v>141232226304</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>18.732826</v>
+        <v>18.916033</v>
       </c>
       <c r="E11" s="34" t="n">
         <v>7.534</v>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>103769882624</v>
+        <v>106055933952</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>19.181416</v>
+        <v>19.603983</v>
       </c>
       <c r="E12" s="34" t="n">
         <v>9.294</v>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>126604894208</v>
+        <v>129104404480</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>38.17919</v>
+        <v>38.93295</v>
       </c>
       <c r="E13" s="34" t="n">
         <v>20.074</v>

--- a/app/reports/HCA_research.xlsx
+++ b/app/reports/HCA_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-27 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-05 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.798</v>
+        <v>0.794</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>472.12</v>
+        <v>494.96</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>388.11</v>
+        <v>410.3301</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.216</v>
+        <v>0.206</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.716</v>
+        <v>0.706</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04647000312805176</v>
+        <v>0.04620999813079834</v>
       </c>
     </row>
     <row r="6">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>1.128</v>
+        <v>1.109</v>
       </c>
     </row>
     <row r="8">
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>1013000000</v>
+        <v>1130000000</v>
       </c>
     </row>
     <row r="34">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>221839807.4772616</v>
+        <v>216501512.3969702</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>388.11</v>
+        <v>410.3301</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>86098247680</v>
+        <v>88837087232</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>13.02</v>
+        <v>13.76</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>8.84</v>
+        <v>8.93</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>128068501504</v>
+        <v>129967718400</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>17.567226</v>
+        <v>13.983516</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>8.579000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>3.357</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>136192475136</v>
+        <v>126610399232</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>46.81579</v>
+        <v>43.521976</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>13.249</v>
+        <v>13.053</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>0.503</v>
+        <v>0.496</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>104586100736</v>
+        <v>103164518400</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>13.7421055</v>
+        <v>16.198112</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>10.361</v>
+        <v>10.904</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>3.614</v>
+        <v>3.553</v>
       </c>
     </row>
     <row r="9">
@@ -1615,17 +1615,15 @@
           <t>McKesson Corporation</t>
         </is>
       </c>
-      <c r="C9" s="33" t="n">
-        <v>100020101120</v>
-      </c>
+      <c r="C9" s="33" t="n"/>
       <c r="D9" s="34" t="n">
-        <v>22.276533</v>
+        <v>22.198854</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>15.576</v>
+        <v>15.394</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>0.266</v>
+        <v>0.263</v>
       </c>
     </row>
     <row r="10">
@@ -1639,17 +1637,15 @@
           <t>Medtronic plc.</t>
         </is>
       </c>
-      <c r="C10" s="33" t="n">
-        <v>108605431808</v>
-      </c>
+      <c r="C10" s="33" t="n"/>
       <c r="D10" s="34" t="n">
-        <v>22.746649</v>
+        <v>23.043125</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>12.576</v>
+        <v>13.015</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>3.494</v>
+        <v>3.616</v>
       </c>
     </row>
     <row r="11">
@@ -1664,16 +1660,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>141232226304</v>
+        <v>145022353408</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>18.916033</v>
+        <v>19.131578</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>7.534</v>
+        <v>7.644</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>3.03</v>
+        <v>3.074</v>
       </c>
     </row>
     <row r="12">
@@ -1688,16 +1684,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>106055933952</v>
+        <v>102686474240</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>19.603983</v>
+        <v>23.040321</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>9.294</v>
+        <v>8.898</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>2.518</v>
+        <v>2.463</v>
       </c>
     </row>
     <row r="13">
@@ -1712,16 +1708,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>129104404480</v>
+        <v>128343547904</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>38.93295</v>
+        <v>34.70954</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>20.074</v>
+        <v>19.366</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>5.496</v>
+        <v>5.529</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/HCA_research.xlsx
+++ b/app/reports/HCA_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-05 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-06 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.794</v>
+        <v>0.793</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>494.96</v>
+        <v>489.75</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>410.3301</v>
+        <v>406.555</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.206</v>
+        <v>0.205</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.706</v>
+        <v>0.705</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04620999813079834</v>
+        <v>0.04668000221252441</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>216501512.3969702</v>
+        <v>216501509.9851189</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>410.3301</v>
+        <v>406.555</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>88837087232</v>
+        <v>88019771392</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>13.76</v>
+        <v>13.63</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>8.93</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>129967718400</v>
+        <v>129661304832</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>13.983516</v>
+        <v>13.981277</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>8.859999999999999</v>
+        <v>8.662000000000001</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>3.41</v>
+        <v>3.334</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>126610399232</v>
+        <v>122999390208</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>43.521976</v>
+        <v>25.435356</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>13.053</v>
+        <v>11.35</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>0.496</v>
+        <v>0.459</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>103164518400</v>
+        <v>104145895424</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>16.198112</v>
+        <v>16.455696</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>10.904</v>
+        <v>10.891</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>3.553</v>
+        <v>3.548</v>
       </c>
     </row>
     <row r="9">
@@ -1617,13 +1617,13 @@
       </c>
       <c r="C9" s="33" t="n"/>
       <c r="D9" s="34" t="n">
-        <v>22.198854</v>
+        <v>22.270954</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>15.394</v>
+        <v>16.211</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>0.263</v>
+        <v>0.277</v>
       </c>
     </row>
     <row r="10">
@@ -1639,13 +1639,13 @@
       </c>
       <c r="C10" s="33" t="n"/>
       <c r="D10" s="34" t="n">
-        <v>23.043125</v>
+        <v>23.010725</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>13.015</v>
+        <v>12.928</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>3.616</v>
+        <v>3.592</v>
       </c>
     </row>
     <row r="11">
@@ -1660,16 +1660,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>145022353408</v>
+        <v>147422052352</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>19.131578</v>
+        <v>34.032894</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>7.644</v>
+        <v>7.847</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>3.074</v>
+        <v>3.127</v>
       </c>
     </row>
     <row r="12">
@@ -1684,16 +1684,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>102686474240</v>
+        <v>103987585024</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>23.040321</v>
+        <v>22.90107</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>8.898</v>
+        <v>8.868</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>2.463</v>
+        <v>2.455</v>
       </c>
     </row>
     <row r="13">
@@ -1708,16 +1708,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>128343547904</v>
+        <v>128395321344</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>34.70954</v>
+        <v>34.723545</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>19.366</v>
+        <v>19.149</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>5.529</v>
+        <v>5.467</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/HCA_research.xlsx
+++ b/app/reports/HCA_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-06 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-07 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.793</v>
+        <v>0.79</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>489.75</v>
+        <v>491.3</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>406.555</v>
+        <v>410.245</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.205</v>
+        <v>0.198</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.705</v>
+        <v>0.698</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04668000221252441</v>
+        <v>0.04654000282287598</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>216501509.9851189</v>
+        <v>216501493.5757901</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>406.555</v>
+        <v>410.245</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>88019771392</v>
+        <v>88818655232</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>13.63</v>
+        <v>13.76</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>9.050000000000001</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>129661304832</v>
+        <v>131101425664</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>13.981277</v>
+        <v>14.136564</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>8.662000000000001</v>
+        <v>8.718</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>3.334</v>
+        <v>3.355</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>122999390208</v>
+        <v>122269564928</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>25.435356</v>
+        <v>25.224274</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>11.35</v>
+        <v>11.128</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>0.459</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>104145895424</v>
+        <v>105798205440</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>16.455696</v>
+        <v>16.664038</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>10.891</v>
+        <v>11.023</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>3.548</v>
+        <v>3.591</v>
       </c>
     </row>
     <row r="9">
@@ -1615,15 +1615,17 @@
           <t>McKesson Corporation</t>
         </is>
       </c>
-      <c r="C9" s="33" t="n"/>
+      <c r="C9" s="33" t="n">
+        <v>102788194304</v>
+      </c>
       <c r="D9" s="34" t="n">
-        <v>22.270954</v>
+        <v>23.63588</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>16.211</v>
+        <v>15.721</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>0.277</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="10">
@@ -1639,13 +1641,13 @@
       </c>
       <c r="C10" s="33" t="n"/>
       <c r="D10" s="34" t="n">
-        <v>23.010725</v>
+        <v>23.077774</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>12.928</v>
+        <v>12.919</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>3.592</v>
+        <v>3.589</v>
       </c>
     </row>
     <row r="11">
@@ -1660,16 +1662,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>147422052352</v>
+        <v>150955851776</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>34.032894</v>
+        <v>34.848686</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>7.847</v>
+        <v>7.935</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>3.127</v>
+        <v>3.162</v>
       </c>
     </row>
     <row r="12">
@@ -1684,16 +1686,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>103987585024</v>
+        <v>104028307456</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>22.90107</v>
+        <v>23.216578</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>8.868</v>
+        <v>8.887</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>2.455</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="13">
@@ -1708,16 +1710,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>128395321344</v>
+        <v>129663041536</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>34.723545</v>
+        <v>35.030052</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>19.149</v>
+        <v>19.17</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>5.467</v>
+        <v>5.473</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/HCA_research.xlsx
+++ b/app/reports/HCA_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-07 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-08 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.79</v>
+        <v>0.786</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>491.3</v>
+        <v>490.63</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>410.245</v>
+        <v>413.36</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.198</v>
+        <v>0.187</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.698</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04654000282287598</v>
+        <v>0.04659999847412109</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>216501493.5757901</v>
+        <v>216501503.8513644</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>410.245</v>
+        <v>413.36</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>88818655232</v>
+        <v>89493061632</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>13.76</v>
+        <v>13.87</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>9.039999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>131101425664</v>
+        <v>132204494848</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>14.136564</v>
+        <v>14.255507</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>8.718</v>
+        <v>8.779</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>3.355</v>
+        <v>3.379</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>122269564928</v>
+        <v>122397458432</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>25.224274</v>
+        <v>25.25066</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>11.128</v>
+        <v>11.088</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>0.45</v>
+        <v>0.448</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>105798205440</v>
+        <v>106068582400</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>16.664038</v>
+        <v>16.706623</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>11.023</v>
+        <v>11.169</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>3.591</v>
+        <v>3.639</v>
       </c>
     </row>
     <row r="9">
@@ -1616,13 +1616,13 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>102788194304</v>
+        <v>101384650752</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>23.63588</v>
+        <v>23.313137</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>15.721</v>
+        <v>15.692</v>
       </c>
       <c r="F9" s="34" t="n">
         <v>0.27</v>
@@ -1641,13 +1641,13 @@
       </c>
       <c r="C10" s="33" t="n"/>
       <c r="D10" s="34" t="n">
-        <v>23.077774</v>
+        <v>23.367292</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>12.919</v>
+        <v>13.076</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>3.589</v>
+        <v>3.633</v>
       </c>
     </row>
     <row r="11">
@@ -1662,16 +1662,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>150955851776</v>
+        <v>152523259904</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>34.848686</v>
+        <v>35.210526</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>7.935</v>
+        <v>8.061</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>3.162</v>
+        <v>3.212</v>
       </c>
     </row>
     <row r="12">
@@ -1686,16 +1686,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>104028307456</v>
+        <v>104136130560</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>23.216578</v>
+        <v>23.24064</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>8.887</v>
+        <v>8.988</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>2.46</v>
+        <v>2.488</v>
       </c>
     </row>
     <row r="13">
@@ -1710,16 +1710,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>129663041536</v>
+        <v>130042773504</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>35.030052</v>
+        <v>35.096275</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>19.17</v>
+        <v>19.253</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>5.473</v>
+        <v>5.496</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/HCA_research.xlsx
+++ b/app/reports/HCA_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-08 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-09 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/HCA_research.xlsx
+++ b/app/reports/HCA_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-09 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-15 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.786</v>
+        <v>0.792</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>490.63</v>
+        <v>486.69</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>413.36</v>
+        <v>404.68</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.187</v>
+        <v>0.203</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.703</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04659999847412109</v>
+        <v>0.04696000099182129</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>216501503.8513644</v>
+        <v>216501495.0677078</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>413.36</v>
+        <v>404.68</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>89493061632</v>
+        <v>87613825024</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>13.87</v>
+        <v>13.57</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>9.1</v>
+        <v>8.98</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>132204494848</v>
+        <v>130386477056</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>14.255507</v>
+        <v>14.059472</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>8.779</v>
+        <v>8.683</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>3.379</v>
+        <v>3.342</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>122397458432</v>
+        <v>124264767488</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>25.25066</v>
+        <v>25.635885</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>11.088</v>
+        <v>11.2</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>0.448</v>
+        <v>0.453</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>106068582400</v>
+        <v>99178938368</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>16.706623</v>
+        <v>15.572327</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>11.169</v>
+        <v>10.532</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>3.639</v>
+        <v>3.431</v>
       </c>
     </row>
     <row r="9">
@@ -1616,13 +1616,13 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>101384650752</v>
+        <v>101317025792</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>23.313137</v>
+        <v>23.310087</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>15.692</v>
+        <v>15.682</v>
       </c>
       <c r="F9" s="34" t="n">
         <v>0.27</v>
@@ -1641,13 +1641,13 @@
       </c>
       <c r="C10" s="33" t="n"/>
       <c r="D10" s="34" t="n">
-        <v>23.367292</v>
+        <v>24.469168</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>13.076</v>
+        <v>13.597</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>3.633</v>
+        <v>3.778</v>
       </c>
     </row>
     <row r="11">
@@ -1662,16 +1662,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>152523259904</v>
+        <v>152694259712</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>35.210526</v>
+        <v>35.25</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>8.061</v>
+        <v>8.067</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>3.212</v>
+        <v>3.215</v>
       </c>
     </row>
     <row r="12">
@@ -1686,16 +1686,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>104136130560</v>
+        <v>104759132160</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>23.24064</v>
+        <v>23.37968</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>8.988</v>
+        <v>9.034000000000001</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>2.488</v>
+        <v>2.501</v>
       </c>
     </row>
     <row r="13">
@@ -1710,16 +1710,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>130042773504</v>
+        <v>130111815680</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>35.096275</v>
+        <v>35.224297</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>19.253</v>
+        <v>19.263</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>5.496</v>
+        <v>5.499</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/HCA_research.xlsx
+++ b/app/reports/HCA_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-15 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-16 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/HCA_research.xlsx
+++ b/app/reports/HCA_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-16 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-18 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.792</v>
+        <v>0.777</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>486.69</v>
+        <v>484.95</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>404.68</v>
+        <v>416.15</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.203</v>
+        <v>0.165</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.703</v>
+        <v>0.665</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04696000099182129</v>
+        <v>0.04711999893188477</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>216501495.0677078</v>
+        <v>216501498.8633906</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>404.68</v>
+        <v>416.15</v>
       </c>
     </row>
     <row r="38">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>87613825024</v>
+        <v>90097098752</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>13.57</v>
+        <v>13.96</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>8.98</v>
+        <v>8.99</v>
       </c>
       <c r="F5" s="32" t="n">
         <v>1.81</v>
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>130386477056</v>
+        <v>135197065216</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>14.059472</v>
+        <v>14.578194</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>8.683</v>
+        <v>8.77</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>3.342</v>
+        <v>3.375</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>124264767488</v>
+        <v>121105711104</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>25.635885</v>
+        <v>24.984169</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>11.2</v>
+        <v>10.958</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>0.453</v>
+        <v>0.443</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>99178938368</v>
+        <v>102623764480</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>15.572327</v>
+        <v>15.863777</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>10.532</v>
+        <v>10.672</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>3.431</v>
+        <v>3.477</v>
       </c>
     </row>
     <row r="9">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>101317025792</v>
+        <v>102412394496</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>23.310087</v>
+        <v>23.536844</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>15.682</v>
+        <v>15.532</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>0.27</v>
+        <v>0.267</v>
       </c>
     </row>
     <row r="10">
@@ -1639,15 +1639,17 @@
           <t>Medtronic plc.</t>
         </is>
       </c>
-      <c r="C10" s="33" t="n"/>
+      <c r="C10" s="33" t="n">
+        <v>118474579968</v>
+      </c>
       <c r="D10" s="34" t="n">
-        <v>24.469168</v>
+        <v>24.813673</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>13.597</v>
+        <v>13.512</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>3.778</v>
+        <v>3.754</v>
       </c>
     </row>
     <row r="11">
@@ -1662,16 +1664,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>152694259712</v>
+        <v>155044233216</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>35.25</v>
+        <v>35.7925</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>8.067</v>
+        <v>8.085000000000001</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>3.215</v>
+        <v>3.222</v>
       </c>
     </row>
     <row r="12">
@@ -1686,16 +1688,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>104759132160</v>
+        <v>107739201536</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>23.37968</v>
+        <v>24.04476</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>9.034000000000001</v>
+        <v>9.156000000000001</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>2.501</v>
+        <v>2.535</v>
       </c>
     </row>
     <row r="13">
@@ -1710,16 +1712,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>130111815680</v>
+        <v>128698343424</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>35.224297</v>
+        <v>34.769432</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>19.263</v>
+        <v>18.871</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>5.499</v>
+        <v>5.387</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/HCA_research.xlsx
+++ b/app/reports/HCA_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-18 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-19 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.777</v>
+        <v>0.783</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>484.95</v>
+        <v>489.09</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>416.15</v>
+        <v>414.7</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.165</v>
+        <v>0.179</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.665</v>
+        <v>0.679</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04711999893188477</v>
+        <v>0.04674000263214111</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>216501498.8633906</v>
+        <v>216501502.5801784</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>416.15</v>
+        <v>414.7</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>90097098752</v>
+        <v>89783173120</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>13.96</v>
+        <v>13.91</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>8.99</v>
+        <v>9.08</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>135197065216</v>
+        <v>137392988160</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>14.578194</v>
+        <v>14.814979</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>8.77</v>
+        <v>8.923</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>3.375</v>
+        <v>3.434</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>121105711104</v>
+        <v>120421449728</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>24.984169</v>
+        <v>24.843008</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>10.958</v>
+        <v>11.027</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>0.443</v>
+        <v>0.446</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>102623764480</v>
+        <v>104866906112</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>15.863777</v>
+        <v>16.413794</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>10.672</v>
+        <v>10.834</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>3.477</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="9">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>102412394496</v>
+        <v>100850663424</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>23.536844</v>
+        <v>23.196568</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>15.532</v>
+        <v>15.686</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>0.267</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="10">
@@ -1640,16 +1640,16 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>118474579968</v>
+        <v>119870201856</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>24.813673</v>
+        <v>25.107239</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>13.512</v>
+        <v>13.701</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>3.754</v>
+        <v>3.806</v>
       </c>
     </row>
     <row r="11">
@@ -1664,16 +1664,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>155044233216</v>
+        <v>160360316928</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>35.7925</v>
+        <v>37.019737</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>8.085000000000001</v>
+        <v>8.170999999999999</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>3.222</v>
+        <v>3.256</v>
       </c>
     </row>
     <row r="12">
@@ -1688,16 +1688,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>107739201536</v>
+        <v>109527441408</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>24.04476</v>
+        <v>24.44385</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>9.156000000000001</v>
+        <v>9.255000000000001</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>2.535</v>
+        <v>2.562</v>
       </c>
     </row>
     <row r="13">
@@ -1712,16 +1712,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>128698343424</v>
+        <v>130660327424</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>34.769432</v>
+        <v>35.3361</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>18.871</v>
+        <v>18.855</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>5.387</v>
+        <v>5.383</v>
       </c>
     </row>
     <row r="15">
